--- a/Tables/G_TutorialInfoTable.xlsx
+++ b/Tables/G_TutorialInfoTable.xlsx
@@ -338,9 +338,14 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="14.88"/>
-    <col customWidth="1" min="2" max="5" width="12.63"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="5.5"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="10.63"/>
     <col customWidth="1" min="6" max="7" width="14.13"/>
-    <col customWidth="1" min="8" max="9" width="12.63"/>
+    <col customWidth="1" min="8" max="8" width="10.88"/>
+    <col customWidth="1" min="9" max="9" width="5.88"/>
+    <col customWidth="1" min="10" max="28" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10106,9 +10111,14 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="14.88"/>
-    <col customWidth="1" min="2" max="5" width="12.63"/>
+    <col customWidth="1" min="2" max="2" width="7.13"/>
+    <col customWidth="1" min="3" max="3" width="5.5"/>
+    <col customWidth="1" min="4" max="4" width="4.75"/>
+    <col customWidth="1" min="5" max="5" width="10.63"/>
     <col customWidth="1" min="6" max="7" width="14.13"/>
-    <col customWidth="1" min="8" max="9" width="12.63"/>
+    <col customWidth="1" min="8" max="8" width="10.88"/>
+    <col customWidth="1" min="9" max="9" width="5.88"/>
+    <col customWidth="1" min="10" max="28" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/Tables/G_TutorialInfoTable.xlsx
+++ b/Tables/G_TutorialInfoTable.xlsx
@@ -29636,15 +29636,15 @@
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
       <c r="J2" s="10">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6))</f>
         <v>0</v>
       </c>
       <c r="K2" s="10">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)-1</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)-1)</f>
         <v>-1</v>
       </c>
       <c r="L2" s="10">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)+1</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)+1)</f>
         <v>1</v>
       </c>
       <c r="M2" s="5">
@@ -44437,15 +44437,15 @@
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
       <c r="J2" s="10">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6))</f>
         <v>100000000</v>
       </c>
       <c r="K2" s="10">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)-1</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)-1)</f>
         <v>99999999</v>
       </c>
       <c r="L2" s="10">
-        <f>($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)+1</f>
+        <f>IF($A2="", -1, ($B2*README!$C$2)+($C2*README!$C$3)+($D2*README!$C$4)+($E2*README!$C$5)+($F2*README!$C$6)+1)</f>
         <v>100000001</v>
       </c>
       <c r="M2" s="5">
